--- a/Excel/InfiniteConfig.xlsx
+++ b/Excel/InfiniteConfig.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="35">
   <si>
     <t>#</t>
   </si>
@@ -1544,12 +1544,6 @@
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:23">
-      <c r="A8" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>0</v>
-      </c>
       <c r="C8" s="1">
         <v>3</v>
       </c>
